--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -12605,7 +12605,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>KG모빌리언스</t>
+          <t>KG파이낸셜</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -16521,7 +16521,7 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>씨어스테크놀로지</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
@@ -17757,7 +17757,7 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>엔씨소프트</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -9849,7 +9849,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>코오롱ENP</t>
+          <t>코오롱이앤피</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -20485,7 +20485,7 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>티웨이항공</t>
+          <t>트리니티항공</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -829,6 +829,7 @@
           <t>140410</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>2026-02-05 23:00:02</t>
@@ -2045,6 +2046,7 @@
           <t>024850</t>
         </is>
       </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>2026-02-05 23:27:40</t>
@@ -2090,6 +2092,7 @@
           <t>115450</t>
         </is>
       </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>2026-02-05 23:28:45</t>
@@ -2110,6 +2113,7 @@
           <t>403870</t>
         </is>
       </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>2026-02-05 23:29:20</t>
@@ -2255,6 +2259,7 @@
           <t>119650</t>
         </is>
       </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>2026-02-05 23:32:41</t>
@@ -2546,6 +2551,7 @@
           <t>222160</t>
         </is>
       </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>2026-02-05 23:39:45</t>
@@ -2666,6 +2672,7 @@
           <t>091340</t>
         </is>
       </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>2026-02-05 23:42:42</t>
@@ -3053,7 +3060,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>TPC</t>
+          <t>TPC로보틱스</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3328,6 +3335,7 @@
           <t>024910</t>
         </is>
       </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
           <t>2026-02-05 23:57:47</t>
@@ -3719,6 +3727,7 @@
           <t>060480</t>
         </is>
       </c>
+      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>2026-02-06 00:08:15</t>
@@ -3764,6 +3773,7 @@
           <t>007690</t>
         </is>
       </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>2026-02-06 00:09:25</t>
@@ -4609,6 +4619,7 @@
           <t>067080</t>
         </is>
       </c>
+      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
           <t>2026-02-06 00:28:55</t>
@@ -4829,6 +4840,7 @@
           <t>023450</t>
         </is>
       </c>
+      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
           <t>2026-02-06 00:34:04</t>
@@ -4899,6 +4911,7 @@
           <t>026960</t>
         </is>
       </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
           <t>2026-02-06 00:35:46</t>
@@ -4919,6 +4932,7 @@
           <t>002210</t>
         </is>
       </c>
+      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
           <t>2026-02-06 00:36:19</t>
@@ -5635,6 +5649,7 @@
           <t>199730</t>
         </is>
       </c>
+      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
           <t>2026-02-06 00:55:05</t>
@@ -5805,6 +5820,7 @@
           <t>310210</t>
         </is>
       </c>
+      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
           <t>2026-02-06 00:59:00</t>
@@ -5871,6 +5887,7 @@
         </is>
       </c>
       <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
           <t>2026-02-06 01:00:38</t>
@@ -6191,6 +6208,7 @@
           <t>419120</t>
         </is>
       </c>
+      <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
           <t>2026-02-06 01:08:05</t>
@@ -6236,6 +6254,7 @@
           <t>419050</t>
         </is>
       </c>
+      <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
           <t>2026-02-06 01:09:15</t>
@@ -7281,6 +7300,7 @@
           <t>318160</t>
         </is>
       </c>
+      <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
           <t>2026-02-06 01:33:26</t>
@@ -7301,6 +7321,7 @@
           <t>308430</t>
         </is>
       </c>
+      <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
           <t>2026-02-06 01:33:55</t>
@@ -8834,7 +8855,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>에코바이오</t>
+          <t>에코심플렉스</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -8892,6 +8913,7 @@
           <t>101360</t>
         </is>
       </c>
+      <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
           <t>2026-02-06 02:11:02</t>
@@ -9012,6 +9034,7 @@
           <t>373200</t>
         </is>
       </c>
+      <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
           <t>2026-02-06 02:13:54</t>
@@ -9307,6 +9330,7 @@
           <t>053280</t>
         </is>
       </c>
+      <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
           <t>2026-02-06 02:20:34</t>
@@ -9502,6 +9526,7 @@
           <t>131030</t>
         </is>
       </c>
+      <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
           <t>2026-02-06 02:25:04</t>
@@ -10593,6 +10618,7 @@
           <t>037330</t>
         </is>
       </c>
+      <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
           <t>2026-02-06 02:50:09</t>
@@ -11538,6 +11564,7 @@
           <t>000650</t>
         </is>
       </c>
+      <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
           <t>2026-02-06 03:12:02</t>
@@ -12108,6 +12135,7 @@
           <t>082660</t>
         </is>
       </c>
+      <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr">
         <is>
           <t>2026-02-06 03:25:01</t>
@@ -12428,6 +12456,7 @@
           <t>445680</t>
         </is>
       </c>
+      <c r="C488" t="inlineStr"/>
       <c r="D488" t="inlineStr">
         <is>
           <t>2026-02-06 03:32:15</t>
@@ -12673,6 +12702,7 @@
           <t>073640</t>
         </is>
       </c>
+      <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr">
         <is>
           <t>2026-02-06 03:37:47</t>
@@ -13468,6 +13498,7 @@
           <t>371950</t>
         </is>
       </c>
+      <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr">
         <is>
           <t>2026-02-06 03:55:43</t>
@@ -13663,6 +13694,7 @@
           <t>033790</t>
         </is>
       </c>
+      <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr">
         <is>
           <t>2026-02-06 04:00:06</t>
@@ -14679,6 +14711,7 @@
           <t>016790</t>
         </is>
       </c>
+      <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr">
         <is>
           <t>2026-02-06 04:23:48</t>
@@ -15249,6 +15282,7 @@
           <t>092780</t>
         </is>
       </c>
+      <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
           <t>2026-02-06 04:36:44</t>
@@ -15636,6 +15670,7 @@
           <t>003620</t>
         </is>
       </c>
+      <c r="C618" t="inlineStr"/>
       <c r="D618" t="inlineStr">
         <is>
           <t>2026-02-06 04:46:37</t>
@@ -15706,6 +15741,7 @@
           <t>058860</t>
         </is>
       </c>
+      <c r="C621" t="inlineStr"/>
       <c r="D621" t="inlineStr">
         <is>
           <t>2026-02-06 04:48:20</t>
@@ -17035,6 +17071,7 @@
           <t>389650</t>
         </is>
       </c>
+      <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr">
         <is>
           <t>2026-02-06 05:20:24</t>
@@ -17505,6 +17542,7 @@
           <t>084670</t>
         </is>
       </c>
+      <c r="C694" t="inlineStr"/>
       <c r="D694" t="inlineStr">
         <is>
           <t>2026-02-06 05:31:53</t>
@@ -17675,6 +17713,7 @@
           <t>176750</t>
         </is>
       </c>
+      <c r="C701" t="inlineStr"/>
       <c r="D701" t="inlineStr">
         <is>
           <t>2026-02-06 05:36:16</t>
@@ -17745,6 +17784,7 @@
           <t>376300</t>
         </is>
       </c>
+      <c r="C704" t="inlineStr"/>
       <c r="D704" t="inlineStr">
         <is>
           <t>2026-02-06 05:38:02</t>
@@ -17890,6 +17930,7 @@
           <t>141080</t>
         </is>
       </c>
+      <c r="C710" t="inlineStr"/>
       <c r="D710" t="inlineStr">
         <is>
           <t>2026-02-06 05:43:46</t>
@@ -18160,6 +18201,7 @@
           <t>021880</t>
         </is>
       </c>
+      <c r="C721" t="inlineStr"/>
       <c r="D721" t="inlineStr">
         <is>
           <t>2026-02-06 05:49:49</t>
@@ -19005,6 +19047,7 @@
           <t>001360</t>
         </is>
       </c>
+      <c r="C755" t="inlineStr"/>
       <c r="D755" t="inlineStr">
         <is>
           <t>2026-02-06 06:09:09</t>
@@ -19225,6 +19268,7 @@
           <t>0013V0</t>
         </is>
       </c>
+      <c r="C764" t="inlineStr"/>
       <c r="D764" t="inlineStr">
         <is>
           <t>2026-02-06 06:14:11</t>
@@ -19770,6 +19814,7 @@
           <t>068760</t>
         </is>
       </c>
+      <c r="C786" t="inlineStr"/>
       <c r="D786" t="inlineStr">
         <is>
           <t>2026-02-06 06:26:40</t>
@@ -21015,6 +21060,7 @@
           <t>476830</t>
         </is>
       </c>
+      <c r="C836" t="inlineStr"/>
       <c r="D836" t="inlineStr">
         <is>
           <t>2026-02-06 06:54:31</t>
@@ -23356,6 +23402,7 @@
           <t>079950</t>
         </is>
       </c>
+      <c r="C930" t="inlineStr"/>
       <c r="D930" t="inlineStr">
         <is>
           <t>2026-02-06 08:20:12</t>
@@ -23451,6 +23498,7 @@
           <t>115310</t>
         </is>
       </c>
+      <c r="C934" t="inlineStr"/>
       <c r="D934" t="inlineStr">
         <is>
           <t>2026-02-06 08:22:33</t>
@@ -23571,6 +23619,7 @@
           <t>081000</t>
         </is>
       </c>
+      <c r="C939" t="inlineStr"/>
       <c r="D939" t="inlineStr">
         <is>
           <t>2026-02-06 08:25:18</t>
@@ -23816,6 +23865,7 @@
           <t>054950</t>
         </is>
       </c>
+      <c r="C949" t="inlineStr"/>
       <c r="D949" t="inlineStr">
         <is>
           <t>2026-02-06 08:31:14</t>
@@ -24061,6 +24111,7 @@
           <t>109070</t>
         </is>
       </c>
+      <c r="C959" t="inlineStr"/>
       <c r="D959" t="inlineStr">
         <is>
           <t>2026-02-06 08:36:48</t>
@@ -24456,6 +24507,7 @@
           <t>210120</t>
         </is>
       </c>
+      <c r="C975" t="inlineStr"/>
       <c r="D975" t="inlineStr">
         <is>
           <t>2026-02-06 08:46:16</t>
@@ -25022,6 +25074,7 @@
           <t>494120</t>
         </is>
       </c>
+      <c r="C998" t="inlineStr"/>
       <c r="D998" t="inlineStr">
         <is>
           <t>2026-02-06 08:59:14</t>
@@ -25292,6 +25345,7 @@
           <t>200230</t>
         </is>
       </c>
+      <c r="C1009" t="inlineStr"/>
       <c r="D1009" t="inlineStr">
         <is>
           <t>2026-02-06 09:05:27</t>

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -17459,7 +17459,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>대성파인텍</t>
+          <t>디에스엠</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -20502,7 +20502,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>씨메스</t>
+          <t>씨메스로보틱스</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -9664,7 +9664,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>위너스</t>
+          <t>위너스일렉</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -3786,7 +3786,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>국전약품</t>
+          <t>국전</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10110,7 +10110,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>유투바이오</t>
+          <t>지구홀딩스</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -6592,7 +6592,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>삼화페인트공업</t>
+          <t>SP삼화</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -1688,7 +1688,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>시알홀딩스</t>
+          <t>CR홀딩스</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>F&amp;F 홀딩스</t>
+          <t>F&amp;F홀딩스</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2226,7 +2226,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>케이씨티시</t>
+          <t>KCTC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5145,10 +5145,14 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>동양철관</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr"/>
+          <t>KBI동양철관</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>008970</t>
+        </is>
+      </c>
       <c r="C193" t="inlineStr">
         <is>
           <t>#알래스카 LNG 사업 #수자원/수처리 #강관/가스관 #대왕고래 #철강/철근</t>
@@ -6517,7 +6521,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>삼화전자공업</t>
+          <t>삼화전자</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6542,7 +6546,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>삼화콘덴서공업</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -10085,7 +10089,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>유진증권</t>
+          <t>유진투자증권</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -13686,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -13957,7 +13961,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>한국ANKOR유전</t>
+          <t>한국투자ANKOR유전해외자원개발특별자산투자회사1호(지분증권)</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -14057,7 +14061,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>한국석유공업</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -14107,7 +14111,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>한국전력공사</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -14357,7 +14361,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>한신기계공업</t>
+          <t>한신기계</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -14999,7 +15003,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>휴니드테크놀러지스</t>
+          <t>휴니드</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -15683,7 +15687,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>케이티앤지</t>
+          <t>KT&amp;G</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -16296,7 +16300,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>에스케이바이오팜</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -16638,7 +16642,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>계룡건설산업</t>
+          <t>계룡건설</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -17847,7 +17851,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>롯데칠성음료</t>
+          <t>롯데칠성</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -19110,7 +19114,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>삼성화재해상보험</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
@@ -20177,7 +20181,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>신세계I&amp;C</t>
+          <t>신세계 I&amp;C</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -21998,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>엑스큐어</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -13690,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>엑스큐어</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -13690,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>엑스큐어</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -23298,7 +23298,7 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>이스트아시아홀딩스</t>
+          <t>딥커머스</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -11535,7 +11535,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>차백신연구소</t>
+          <t>아리바이오랩</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -13690,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>엑스큐어</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -13690,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>엑스큐어</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -942,7 +942,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>씨아이에스</t>
+          <t>SFA넥셀</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -13690,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>엑스큐어</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -10064,7 +10064,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>유일에너테크</t>
+          <t>성원에너텍</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -13690,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>엑스큐어</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -2543,7 +2543,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NPX</t>
+          <t>엔피엑스</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -13690,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>엑스큐어</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -5195,7 +5195,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>동원금속</t>
+          <t>동원모빌리티</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -13690,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -14211,7 +14211,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>한글과컴퓨터</t>
+          <t>한컴</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>엑스큐어</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -22798,7 +22798,7 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>우정바이오</t>
+          <t>콜마바이오텍</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -7338,7 +7338,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>소룩스</t>
+          <t>아리바이오홀딩스</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13690,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>엑스큐어</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -13690,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>퀀텀레일</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -8559,7 +8559,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>압타머사이언스</t>
+          <t>츌립앤사이언스</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -13690,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>퀀텀레일</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -13690,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>퀀텀레일</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
